--- a/Design Input File_Student_Blank_V26-01.xlsx
+++ b/Design Input File_Student_Blank_V26-01.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leokey/Documents/MATLAB/ASEN 2502/Student ASEN 2502 Design Code v2/Design Input Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AE67DA-A774-DA47-A03B-FBCB4BD319F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E819A2-D3E6-6540-AFB4-4B64606A8EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15100" yWindow="680" windowWidth="15140" windowHeight="17520" activeTab="1" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
   </bookViews>
@@ -1134,7 +1134,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>John Mah:</t>
         </r>
@@ -1143,7 +1143,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 User specified material density</t>
@@ -1158,7 +1158,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>John Mah:</t>
         </r>
@@ -1167,7 +1167,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 User specified material density</t>
@@ -1201,7 +1201,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="225">
   <si>
     <t>Worksheet</t>
   </si>
@@ -1867,6 +1867,15 @@
   </si>
   <si>
     <t>AF1</t>
+  </si>
+  <si>
+    <t>Config2</t>
+  </si>
+  <si>
+    <t>NACA 4412</t>
+  </si>
+  <si>
+    <t>NACA 0012</t>
   </si>
 </sst>
 </file>
@@ -1876,7 +1885,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1910,19 +1919,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
@@ -2129,13 +2125,13 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4175,10 +4171,144 @@
         <v>216</v>
       </c>
     </row>
+    <row r="3" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>18</v>
+      </c>
+      <c r="D3">
+        <v>1.3</v>
+      </c>
+      <c r="E3">
+        <v>0.12</v>
+      </c>
+      <c r="F3">
+        <v>10.83</v>
+      </c>
+      <c r="G3">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="H3">
+        <v>4.5240000000000002E-2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1.03</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M3">
+        <v>0.1875</v>
+      </c>
+      <c r="N3">
+        <v>0.375</v>
+      </c>
+      <c r="O3">
+        <v>12</v>
+      </c>
+      <c r="P3">
+        <v>0.7</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="T3" t="s">
+        <v>209</v>
+      </c>
+      <c r="U3">
+        <v>0.03</v>
+      </c>
+      <c r="V3">
+        <v>0.06</v>
+      </c>
+      <c r="W3">
+        <v>4</v>
+      </c>
+      <c r="X3">
+        <v>0.8</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="AA3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>209</v>
+      </c>
+      <c r="AC3">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AD3">
+        <v>0.03</v>
+      </c>
+      <c r="AE3">
+        <v>1.8</v>
+      </c>
+      <c r="AF3">
+        <v>0.6</v>
+      </c>
+      <c r="AG3">
+        <v>20</v>
+      </c>
+      <c r="AH3">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="AI3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>216</v>
+      </c>
+    </row>
     <row r="21" s="22" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L51 T2:T51 AJ2:AJ51 AR2:AR51 AB2:AB51" xr:uid="{F18DD44F-5AC9-42F9-970E-83AFBD39DB9D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB51 AR2:AR51 AJ2:AJ51 T2:T51 L2:L51" xr:uid="{F18DD44F-5AC9-42F9-970E-83AFBD39DB9D}">
       <formula1>MATERIALS</formula1>
     </dataValidation>
   </dataValidations>
@@ -4521,24 +4651,159 @@
       </c>
     </row>
     <row r="3" spans="1:51" x14ac:dyDescent="0.2">
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
-      <c r="AB3" s="13"/>
-      <c r="AC3" s="13"/>
-      <c r="AD3" s="13"/>
-      <c r="AE3" s="13"/>
-      <c r="AF3" s="13"/>
-      <c r="AG3" s="13"/>
-      <c r="AH3" s="13"/>
-      <c r="AI3" s="13"/>
-      <c r="AJ3" s="13"/>
-      <c r="AK3" s="13"/>
-      <c r="AL3" s="13"/>
-      <c r="AM3" s="13"/>
-      <c r="AN3" s="13"/>
-      <c r="AO3" s="13"/>
+      <c r="A3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3">
+        <v>0.12</v>
+      </c>
+      <c r="D3">
+        <v>0.3</v>
+      </c>
+      <c r="E3">
+        <v>-0.14660000000000001</v>
+      </c>
+      <c r="F3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G3">
+        <v>0.13420000000000001</v>
+      </c>
+      <c r="H3">
+        <v>0.25409999999999999</v>
+      </c>
+      <c r="I3">
+        <v>0.35830000000000001</v>
+      </c>
+      <c r="J3">
+        <v>0.49380000000000002</v>
+      </c>
+      <c r="K3">
+        <v>0.5988</v>
+      </c>
+      <c r="L3">
+        <v>0.70379999999999998</v>
+      </c>
+      <c r="M3">
+        <v>0.80840000000000001</v>
+      </c>
+      <c r="N3">
+        <v>0.91269999999999996</v>
+      </c>
+      <c r="O3">
+        <v>1.0156000000000001</v>
+      </c>
+      <c r="P3">
+        <v>1.1122000000000001</v>
+      </c>
+      <c r="Q3">
+        <v>1.2001999999999999</v>
+      </c>
+      <c r="R3">
+        <v>1.2799</v>
+      </c>
+      <c r="S3">
+        <v>1.3267</v>
+      </c>
+      <c r="T3">
+        <v>1.3274999999999999</v>
+      </c>
+      <c r="U3">
+        <v>1.3429</v>
+      </c>
+      <c r="V3">
+        <v>1.3641000000000001</v>
+      </c>
+      <c r="W3">
+        <v>1.4467000000000001</v>
+      </c>
+      <c r="X3" s="13">
+        <v>1.934E-2</v>
+      </c>
+      <c r="Y3" s="13">
+        <v>1.6379999999999999E-2</v>
+      </c>
+      <c r="Z3" s="13">
+        <v>1.4370000000000001E-2</v>
+      </c>
+      <c r="AA3" s="13">
+        <v>1.274E-2</v>
+      </c>
+      <c r="AB3" s="13">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="AC3" s="13">
+        <v>1.005E-2</v>
+      </c>
+      <c r="AD3" s="13">
+        <v>1.039E-2</v>
+      </c>
+      <c r="AE3" s="13">
+        <v>1.0970000000000001E-2</v>
+      </c>
+      <c r="AF3" s="13">
+        <v>1.171E-2</v>
+      </c>
+      <c r="AG3" s="13">
+        <v>1.256E-2</v>
+      </c>
+      <c r="AH3" s="13">
+        <v>1.3520000000000001E-2</v>
+      </c>
+      <c r="AI3" s="13">
+        <v>1.444E-2</v>
+      </c>
+      <c r="AJ3" s="13">
+        <v>1.536E-2</v>
+      </c>
+      <c r="AK3" s="13">
+        <v>1.67E-2</v>
+      </c>
+      <c r="AL3" s="13">
+        <v>1.9439999999999999E-2</v>
+      </c>
+      <c r="AM3" s="13">
+        <v>2.555E-2</v>
+      </c>
+      <c r="AN3" s="13">
+        <v>3.209E-2</v>
+      </c>
+      <c r="AO3" s="13">
+        <v>3.9170000000000003E-2</v>
+      </c>
+      <c r="AP3">
+        <v>9.9900000000000006E-3</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>224</v>
+      </c>
+      <c r="AR3">
+        <v>0.12</v>
+      </c>
+      <c r="AS3">
+        <v>0.3</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>224</v>
+      </c>
+      <c r="AU3">
+        <v>0.12</v>
+      </c>
+      <c r="AV3">
+        <v>0.3</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:51" x14ac:dyDescent="0.2">
       <c r="X4" s="13"/>
@@ -4714,27 +4979,69 @@
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
-      <c r="U3" s="4"/>
+      <c r="A3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4">
+        <v>0</v>
+      </c>
+      <c r="U3" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>

--- a/Design Input File_Student_Blank_V26-01.xlsx
+++ b/Design Input File_Student_Blank_V26-01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\claud\Downloads\Student ASEN 2502 Design Code\Student ASEN 2502 Design Code v2\Design Input Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leokey/Documents/MATLAB/ASEN 2502/Student ASEN 2502 Design Code v2/Design Input Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{624A5D01-8DF4-49D7-A41C-CA0DC2217BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249B3FA5-DC23-BC42-ADB8-E4820851C491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
+    <workbookView xWindow="180" yWindow="660" windowWidth="30060" windowHeight="17520" activeTab="2" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="12" r:id="rId1"/>
@@ -348,7 +348,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -357,12 +357,21 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Wing Aspect Ratio</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Wing Aspect Ratio</t>
         </r>
       </text>
     </comment>
@@ -540,7 +549,7 @@
           <rPr>
             <b/>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -549,12 +558,21 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
+            <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Horz Tail 1 Taper Ratio</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Horz Tail 1 Taper Ratio</t>
         </r>
       </text>
     </comment>
@@ -1116,7 +1134,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>John Mah:</t>
         </r>
@@ -1125,7 +1143,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 User specified material density</t>
@@ -1140,7 +1158,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>John Mah:</t>
         </r>
@@ -1149,7 +1167,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 User specified material density</t>
@@ -1183,7 +1201,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="225">
   <si>
     <t>Worksheet</t>
   </si>
@@ -1842,19 +1860,22 @@
     <t>kg/m^2</t>
   </si>
   <si>
-    <t>NACA 0010</t>
-  </si>
-  <si>
-    <t>MH32</t>
-  </si>
-  <si>
-    <t>Airy Potter</t>
-  </si>
-  <si>
-    <t>NACA4412</t>
+    <t>HS1</t>
+  </si>
+  <si>
+    <t>VS1</t>
+  </si>
+  <si>
+    <t>AF1</t>
+  </si>
+  <si>
+    <t>Config2</t>
   </si>
   <si>
     <t>NACA 4412</t>
+  </si>
+  <si>
+    <t>NACA 0012</t>
   </si>
 </sst>
 </file>
@@ -1864,7 +1885,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1900,20 +1921,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
+      <sz val="8"/>
+      <color rgb="FF555555"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <color indexed="81"/>
+      <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1974,8 +2001,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2009,11 +2042,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFA3A3A3"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFA3A3A3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2080,6 +2124,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2673,16 +2726,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D14EA422-282A-4DE2-BD24-B68BB0CEE4E3}">
   <dimension ref="A1:D81"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="108.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="108.83203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -2696,7 +2749,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -2711,7 +2764,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -2725,7 +2778,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -2739,7 +2792,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -2753,7 +2806,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -2767,7 +2820,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
@@ -2781,7 +2834,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
@@ -2795,7 +2848,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
@@ -2809,7 +2862,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
@@ -2823,7 +2876,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
@@ -2837,7 +2890,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>4</v>
       </c>
@@ -2851,7 +2904,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>4</v>
       </c>
@@ -2865,7 +2918,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>4</v>
       </c>
@@ -2879,7 +2932,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>4</v>
       </c>
@@ -2893,7 +2946,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
@@ -2907,7 +2960,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>4</v>
       </c>
@@ -2921,7 +2974,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>4</v>
       </c>
@@ -2935,7 +2988,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>4</v>
       </c>
@@ -2949,7 +3002,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="48" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>4</v>
       </c>
@@ -2963,7 +3016,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>4</v>
       </c>
@@ -2977,7 +3030,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>4</v>
       </c>
@@ -2991,7 +3044,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>4</v>
       </c>
@@ -3005,7 +3058,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>4</v>
       </c>
@@ -3019,7 +3072,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>4</v>
       </c>
@@ -3033,7 +3086,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>4</v>
       </c>
@@ -3047,7 +3100,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>4</v>
       </c>
@@ -3061,7 +3114,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="48" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>4</v>
       </c>
@@ -3075,7 +3128,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>4</v>
       </c>
@@ -3089,7 +3142,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>4</v>
       </c>
@@ -3103,7 +3156,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>4</v>
       </c>
@@ -3117,7 +3170,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>4</v>
       </c>
@@ -3131,7 +3184,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>4</v>
       </c>
@@ -3145,7 +3198,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>4</v>
       </c>
@@ -3159,7 +3212,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>4</v>
       </c>
@@ -3173,7 +3226,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>4</v>
       </c>
@@ -3187,7 +3240,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>4</v>
       </c>
@@ -3201,7 +3254,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>4</v>
       </c>
@@ -3215,7 +3268,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>4</v>
       </c>
@@ -3229,7 +3282,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>4</v>
       </c>
@@ -3243,7 +3296,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>4</v>
       </c>
@@ -3257,7 +3310,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>4</v>
       </c>
@@ -3271,7 +3324,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>4</v>
       </c>
@@ -3285,7 +3338,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>4</v>
       </c>
@@ -3299,7 +3352,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>4</v>
       </c>
@@ -3313,7 +3366,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>54</v>
       </c>
@@ -3327,7 +3380,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>54</v>
       </c>
@@ -3341,7 +3394,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>54</v>
       </c>
@@ -3355,7 +3408,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>54</v>
       </c>
@@ -3369,7 +3422,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>54</v>
       </c>
@@ -3383,7 +3436,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>54</v>
       </c>
@@ -3397,7 +3450,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
@@ -3411,7 +3464,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>54</v>
       </c>
@@ -3425,7 +3478,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>54</v>
       </c>
@@ -3439,7 +3492,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>54</v>
       </c>
@@ -3453,7 +3506,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>54</v>
       </c>
@@ -3467,7 +3520,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>54</v>
       </c>
@@ -3481,7 +3534,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>54</v>
       </c>
@@ -3495,7 +3548,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>54</v>
       </c>
@@ -3509,7 +3562,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>54</v>
       </c>
@@ -3523,7 +3576,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>85</v>
       </c>
@@ -3538,7 +3591,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>85</v>
       </c>
@@ -3552,7 +3605,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>85</v>
       </c>
@@ -3566,7 +3619,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>85</v>
       </c>
@@ -3580,7 +3633,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>85</v>
       </c>
@@ -3594,7 +3647,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>85</v>
       </c>
@@ -3608,7 +3661,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>85</v>
       </c>
@@ -3622,7 +3675,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>85</v>
       </c>
@@ -3636,7 +3689,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
         <v>85</v>
       </c>
@@ -3650,7 +3703,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
         <v>85</v>
       </c>
@@ -3664,7 +3717,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
         <v>85</v>
       </c>
@@ -3678,7 +3731,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
         <v>85</v>
       </c>
@@ -3692,7 +3745,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
         <v>85</v>
       </c>
@@ -3706,7 +3759,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
         <v>85</v>
       </c>
@@ -3720,7 +3773,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
         <v>85</v>
       </c>
@@ -3734,7 +3787,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
         <v>85</v>
       </c>
@@ -3748,7 +3801,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
         <v>85</v>
       </c>
@@ -3762,7 +3815,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
         <v>85</v>
       </c>
@@ -3776,7 +3829,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
         <v>85</v>
       </c>
@@ -3790,7 +3843,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
         <v>85</v>
       </c>
@@ -3804,7 +3857,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
         <v>85</v>
       </c>
@@ -3826,31 +3879,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28ADD393-55AB-49FB-9382-D2896E9EB980}">
   <dimension ref="A1:AR21"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="4"/>
-    <col min="2" max="2" width="10.5546875" style="4" customWidth="1"/>
-    <col min="3" max="11" width="8.77734375" style="4"/>
-    <col min="12" max="12" width="15.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.77734375" style="4" customWidth="1"/>
-    <col min="14" max="14" width="8.77734375" style="4"/>
+    <col min="1" max="1" width="8.83203125" style="4"/>
+    <col min="2" max="2" width="10.5" style="4" customWidth="1"/>
+    <col min="3" max="11" width="8.83203125" style="4"/>
+    <col min="12" max="12" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.83203125" style="4" customWidth="1"/>
+    <col min="14" max="14" width="8.83203125" style="4"/>
     <col min="15" max="15" width="12" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="8.77734375" style="4"/>
-    <col min="18" max="18" width="16.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.77734375" style="4"/>
-    <col min="20" max="20" width="15.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="21" max="27" width="8.77734375" style="4"/>
-    <col min="28" max="28" width="15.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="8.77734375" style="4"/>
+    <col min="16" max="17" width="8.83203125" style="4"/>
+    <col min="18" max="18" width="16.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.83203125" style="4"/>
+    <col min="20" max="20" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="27" width="8.83203125" style="4"/>
+    <col min="28" max="28" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="8.83203125" style="4"/>
     <col min="31" max="31" width="12" style="4" bestFit="1" customWidth="1"/>
-    <col min="32" max="35" width="8.77734375" style="4"/>
-    <col min="36" max="36" width="16.77734375" style="4" customWidth="1"/>
-    <col min="37" max="43" width="8.77734375" style="4"/>
-    <col min="44" max="44" width="20.21875" style="4" customWidth="1"/>
-    <col min="45" max="16384" width="8.77734375" style="4"/>
+    <col min="32" max="35" width="8.83203125" style="4"/>
+    <col min="36" max="36" width="16.6640625" style="4" customWidth="1"/>
+    <col min="37" max="43" width="8.83203125" style="4"/>
+    <col min="44" max="44" width="20.33203125" style="4" customWidth="1"/>
+    <col min="45" max="16384" width="8.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>107</v>
       </c>
@@ -3984,12 +4037,12 @@
         <v>150</v>
       </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>151</v>
       </c>
       <c r="B2" s="4">
-        <v>1655</v>
+        <v>100</v>
       </c>
       <c r="C2" s="4">
         <v>20</v>
@@ -4004,7 +4057,7 @@
         <v>9.75</v>
       </c>
       <c r="G2" s="4">
-        <v>2E-3</v>
+        <v>0.02</v>
       </c>
       <c r="H2" s="4">
         <v>8.0399999999999999E-2</v>
@@ -4031,7 +4084,7 @@
         <v>16.5</v>
       </c>
       <c r="P2" s="4">
-        <v>1</v>
+        <v>0.86899999999999999</v>
       </c>
       <c r="Q2" s="4">
         <v>0</v>
@@ -4051,11 +4104,11 @@
       <c r="V2" s="4">
         <v>0.19500000000000001</v>
       </c>
-      <c r="W2" s="4">
-        <v>5.7692310000000004</v>
+      <c r="W2" s="26">
+        <v>5769</v>
       </c>
       <c r="X2" s="4">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Y2" s="4">
         <v>0</v>
@@ -4067,22 +4120,22 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AC2" s="4">
         <v>0.08</v>
       </c>
       <c r="AD2" s="4">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="AE2" s="4">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AF2" s="4">
         <v>0.9</v>
       </c>
       <c r="AG2" s="4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AH2" s="4">
         <v>0.2</v>
@@ -4091,7 +4144,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="AJ2" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AK2" s="4">
         <v>0</v>
@@ -4118,141 +4171,141 @@
         <v>216</v>
       </c>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1655</v>
-      </c>
-      <c r="C3" s="4">
+    <row r="3" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3">
+        <v>100</v>
+      </c>
+      <c r="C3">
+        <v>15</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0.1</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>1.2E-2</v>
+      </c>
+      <c r="H3">
+        <v>7.8499999999999993E-3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>209</v>
+      </c>
+      <c r="M3">
+        <v>8.3299999999999999E-2</v>
+      </c>
+      <c r="N3">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="O3">
+        <v>12</v>
+      </c>
+      <c r="P3">
+        <v>0.7</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="T3" t="s">
+        <v>209</v>
+      </c>
+      <c r="U3">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="V3">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="W3">
+        <v>4</v>
+      </c>
+      <c r="X3">
+        <v>0.8</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>6.7100000000000007E-2</v>
+      </c>
+      <c r="AA3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>209</v>
+      </c>
+      <c r="AC3">
+        <v>0.01</v>
+      </c>
+      <c r="AD3">
+        <v>0.02</v>
+      </c>
+      <c r="AE3">
+        <v>1.8</v>
+      </c>
+      <c r="AF3">
+        <v>0.6</v>
+      </c>
+      <c r="AG3">
         <v>20</v>
       </c>
-      <c r="D3" s="4">
-        <v>0.62</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="F3" s="4">
-        <v>7.75</v>
-      </c>
-      <c r="G3" s="4">
-        <v>2E-3</v>
-      </c>
-      <c r="H3" s="4">
-        <v>0.08</v>
-      </c>
-      <c r="I3" s="4">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4">
-        <v>1.4</v>
-      </c>
-      <c r="K3" s="4">
-        <v>1</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="M3" s="4">
-        <v>0.115</v>
-      </c>
-      <c r="N3" s="4">
-        <v>0.23</v>
-      </c>
-      <c r="O3" s="4">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="P3" s="4">
-        <v>0.4375</v>
-      </c>
-      <c r="Q3" s="4">
-        <v>0</v>
-      </c>
-      <c r="R3" s="4">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4">
+      <c r="AH3">
+        <v>7.4499999999999997E-2</v>
+      </c>
+      <c r="AI3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="T3" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="U3" s="4">
-        <v>1.4E-2</v>
-      </c>
-      <c r="V3" s="4">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="W3" s="4">
-        <v>3.78</v>
-      </c>
-      <c r="X3" s="4">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="4">
-        <v>0.05</v>
-      </c>
-      <c r="AA3" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="AB3" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC3" s="4">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="AD3" s="4">
-        <v>0.12</v>
-      </c>
-      <c r="AE3" s="4">
-        <v>3.78</v>
-      </c>
-      <c r="AF3" s="4">
-        <v>0.44</v>
-      </c>
-      <c r="AG3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="4">
-        <v>0.10299999999999999</v>
-      </c>
-      <c r="AI3" s="4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="AJ3" s="4" t="s">
+      <c r="AJ3" t="s">
+        <v>209</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="s">
         <v>216</v>
       </c>
-      <c r="AK3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AL3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AP3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AQ3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AR3" s="4" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="21" s="22" customFormat="1" x14ac:dyDescent="0.3"/>
+    </row>
+    <row r="21" s="22" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L51 T2:T51 AJ2:AJ51 AR2:AR51 AB2:AB51" xr:uid="{F18DD44F-5AC9-42F9-970E-83AFBD39DB9D}">
@@ -4267,26 +4320,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{538960B4-04F0-4DA1-BF31-3569558CC234}">
   <dimension ref="A1:AY21"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="12"/>
-    <col min="2" max="2" width="11.77734375" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="12"/>
+    <col min="2" max="2" width="11.83203125" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="42" width="8.77734375" style="12"/>
-    <col min="43" max="43" width="11.77734375" style="12" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="8.77734375" style="12"/>
-    <col min="45" max="45" width="9.77734375" style="12" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="10.21875" style="12" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="8.77734375" style="12"/>
-    <col min="48" max="48" width="10.21875" style="12" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="11.77734375" style="12" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.77734375" style="12"/>
-    <col min="51" max="51" width="11.5546875" style="12" customWidth="1"/>
-    <col min="52" max="16384" width="8.77734375" style="12"/>
+    <col min="4" max="4" width="9.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="42" width="8.83203125" style="12"/>
+    <col min="43" max="43" width="11.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.83203125" style="12"/>
+    <col min="45" max="45" width="9.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="10.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="8.83203125" style="12"/>
+    <col min="48" max="48" width="10.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="11.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8.83203125" style="12"/>
+    <col min="51" max="51" width="11.5" style="12" customWidth="1"/>
+    <col min="52" max="16384" width="8.83203125" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>107</v>
       </c>
@@ -4441,130 +4494,130 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:51" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="str">
         <f>Main_Input!A2</f>
         <v>Config1</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="C2" s="12">
-        <v>8.6999999999999994E-2</v>
-      </c>
-      <c r="D2" s="12">
-        <v>0.30199999999999999</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="B2" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="E2" s="25">
         <v>-0.41660000000000003</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="25">
         <v>-0.27339999999999998</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="25">
         <v>-0.125</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="25">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="25">
         <v>0.21360000000000001</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="4">
         <v>0.33119999999999999</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="27">
         <v>0.42630000000000001</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="4">
         <v>0.52410000000000001</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="4">
         <v>0.62360000000000004</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="27">
         <v>0.72170000000000001</v>
       </c>
-      <c r="O2" s="12">
+      <c r="O2" s="27">
         <v>0.8165</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="27">
         <v>0.90590000000000004</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="4">
         <v>0.9889</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="25">
         <v>1.0582</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="25">
         <v>1.1042000000000001</v>
       </c>
-      <c r="T2" s="12">
+      <c r="T2" s="4">
         <v>1.1555</v>
       </c>
-      <c r="U2" s="12">
+      <c r="U2" s="4">
         <v>1.1303000000000001</v>
       </c>
-      <c r="V2" s="12">
+      <c r="V2" s="4">
         <v>1.097</v>
       </c>
       <c r="W2" s="12">
-        <v>1.1555</v>
+        <v>1.155</v>
       </c>
       <c r="X2" s="13">
-        <v>4.0500000000000001E-2</v>
+        <v>4.0489999999999998E-2</v>
       </c>
       <c r="Y2" s="13">
         <v>0.02</v>
       </c>
-      <c r="Z2" s="13">
-        <v>1.44E-2</v>
-      </c>
-      <c r="AA2" s="13">
-        <v>1.0500000000000001E-2</v>
+      <c r="Z2" s="25">
+        <v>1.439E-2</v>
+      </c>
+      <c r="AA2" s="25">
+        <v>1.0540000000000001E-2</v>
       </c>
       <c r="AB2" s="13">
-        <v>9.7999999999999997E-3</v>
+        <v>9.7599999999999996E-3</v>
       </c>
       <c r="AC2" s="13">
-        <v>9.2999999999999992E-3</v>
+        <v>9.3299999999999998E-3</v>
       </c>
       <c r="AD2" s="13">
-        <v>9.1000000000000004E-3</v>
+        <v>9.0600000000000003E-3</v>
       </c>
       <c r="AE2" s="13">
-        <v>8.9999999999999993E-3</v>
-      </c>
-      <c r="AF2" s="13">
-        <v>9.2999999999999992E-3</v>
+        <v>8.9800000000000001E-3</v>
+      </c>
+      <c r="AF2" s="27">
+        <v>9.2800000000000001E-3</v>
       </c>
       <c r="AG2" s="13">
         <v>1.01E-2</v>
       </c>
       <c r="AH2" s="13">
-        <v>1.1299999999999999E-2</v>
+        <v>1.133E-2</v>
       </c>
       <c r="AI2" s="13">
-        <v>1.3100000000000001E-2</v>
+        <v>1.3140000000000001E-2</v>
       </c>
       <c r="AJ2" s="13">
-        <v>1.5699999999999999E-2</v>
-      </c>
-      <c r="AK2" s="13">
-        <v>2.01E-2</v>
+        <v>1.5730000000000001E-2</v>
+      </c>
+      <c r="AK2" s="25">
+        <v>2.0119999999999999E-2</v>
       </c>
       <c r="AL2" s="13">
-        <v>2.7199999999999998E-2</v>
-      </c>
-      <c r="AM2" s="13">
-        <v>3.6400000000000002E-2</v>
-      </c>
-      <c r="AN2" s="13">
-        <v>5.1900000000000002E-2</v>
-      </c>
-      <c r="AO2" s="13">
-        <v>6.2399999999999997E-2</v>
+        <v>2.7230000000000001E-2</v>
+      </c>
+      <c r="AM2" s="25">
+        <v>3.6409999999999998E-2</v>
+      </c>
+      <c r="AN2" s="25">
+        <v>5.1929999999999997E-2</v>
+      </c>
+      <c r="AO2" s="25">
+        <v>6.2429999999999999E-2</v>
       </c>
       <c r="AP2" s="12">
         <v>8.9800000000000001E-3</v>
@@ -4573,186 +4626,186 @@
         <v>219</v>
       </c>
       <c r="AR2" s="12">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="AS2" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="AT2" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="AU2" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="AV2" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="AW2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="12">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3">
+        <v>0.12</v>
+      </c>
+      <c r="D3">
         <v>0.3</v>
       </c>
-      <c r="AT2" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="AU2" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="AV2" s="12">
+      <c r="E3">
+        <v>-0.14660000000000001</v>
+      </c>
+      <c r="F3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G3">
+        <v>0.13420000000000001</v>
+      </c>
+      <c r="H3">
+        <v>0.25409999999999999</v>
+      </c>
+      <c r="I3">
+        <v>0.35830000000000001</v>
+      </c>
+      <c r="J3">
+        <v>0.49380000000000002</v>
+      </c>
+      <c r="K3">
+        <v>0.5988</v>
+      </c>
+      <c r="L3">
+        <v>0.70379999999999998</v>
+      </c>
+      <c r="M3">
+        <v>0.80840000000000001</v>
+      </c>
+      <c r="N3">
+        <v>0.91269999999999996</v>
+      </c>
+      <c r="O3">
+        <v>1.0156000000000001</v>
+      </c>
+      <c r="P3">
+        <v>1.1122000000000001</v>
+      </c>
+      <c r="Q3">
+        <v>1.2001999999999999</v>
+      </c>
+      <c r="R3">
+        <v>1.2799</v>
+      </c>
+      <c r="S3">
+        <v>1.3267</v>
+      </c>
+      <c r="T3">
+        <v>1.3274999999999999</v>
+      </c>
+      <c r="U3">
+        <v>1.3429</v>
+      </c>
+      <c r="V3">
+        <v>1.3641000000000001</v>
+      </c>
+      <c r="W3">
+        <v>1.4467000000000001</v>
+      </c>
+      <c r="X3" s="13">
+        <v>1.934E-2</v>
+      </c>
+      <c r="Y3" s="13">
+        <v>1.6379999999999999E-2</v>
+      </c>
+      <c r="Z3" s="13">
+        <v>1.4370000000000001E-2</v>
+      </c>
+      <c r="AA3" s="13">
+        <v>1.274E-2</v>
+      </c>
+      <c r="AB3" s="13">
+        <v>1.0699999999999999E-2</v>
+      </c>
+      <c r="AC3" s="13">
+        <v>1.005E-2</v>
+      </c>
+      <c r="AD3" s="13">
+        <v>1.039E-2</v>
+      </c>
+      <c r="AE3" s="13">
+        <v>1.0970000000000001E-2</v>
+      </c>
+      <c r="AF3" s="13">
+        <v>1.171E-2</v>
+      </c>
+      <c r="AG3" s="13">
+        <v>1.256E-2</v>
+      </c>
+      <c r="AH3" s="13">
+        <v>1.3520000000000001E-2</v>
+      </c>
+      <c r="AI3" s="13">
+        <v>1.444E-2</v>
+      </c>
+      <c r="AJ3" s="13">
+        <v>1.536E-2</v>
+      </c>
+      <c r="AK3" s="13">
+        <v>1.67E-2</v>
+      </c>
+      <c r="AL3" s="13">
+        <v>1.9439999999999999E-2</v>
+      </c>
+      <c r="AM3" s="13">
+        <v>2.555E-2</v>
+      </c>
+      <c r="AN3" s="13">
+        <v>3.209E-2</v>
+      </c>
+      <c r="AO3" s="13">
+        <v>3.9170000000000003E-2</v>
+      </c>
+      <c r="AP3">
+        <v>9.9900000000000006E-3</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>224</v>
+      </c>
+      <c r="AR3">
+        <v>0.12</v>
+      </c>
+      <c r="AS3">
         <v>0.3</v>
       </c>
-      <c r="AW2" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="AX2" s="12">
-        <v>0</v>
-      </c>
-      <c r="AY2" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="C3" s="12">
+      <c r="AT3" t="s">
+        <v>224</v>
+      </c>
+      <c r="AU3">
         <v>0.12</v>
       </c>
-      <c r="D3" s="12">
+      <c r="AV3">
         <v>0.3</v>
       </c>
-      <c r="E3" s="12">
-        <v>-0.33900000000000002</v>
-      </c>
-      <c r="F3" s="12">
-        <v>-0.17319999999999999</v>
-      </c>
-      <c r="G3" s="12">
-        <v>-1.35E-2</v>
-      </c>
-      <c r="H3" s="12">
-        <v>0.13780000000000001</v>
-      </c>
-      <c r="I3" s="12">
-        <v>0.30109999999999998</v>
-      </c>
-      <c r="J3" s="12">
-        <v>0.4335</v>
-      </c>
-      <c r="K3" s="12">
-        <v>0.56310000000000004</v>
-      </c>
-      <c r="L3" s="12">
-        <v>0.6774</v>
-      </c>
-      <c r="M3" s="12">
-        <v>0.79290000000000005</v>
-      </c>
-      <c r="N3" s="12">
-        <v>0.89570000000000005</v>
-      </c>
-      <c r="O3" s="12">
-        <v>0.99950000000000006</v>
-      </c>
-      <c r="P3" s="12">
-        <v>1.1015999999999999</v>
-      </c>
-      <c r="Q3" s="12">
-        <v>1.1987000000000001</v>
-      </c>
-      <c r="R3" s="12">
-        <v>1.2768999999999999</v>
-      </c>
-      <c r="S3" s="12">
-        <v>1.3281000000000001</v>
-      </c>
-      <c r="T3" s="12">
-        <v>1.3127</v>
-      </c>
-      <c r="U3" s="12">
-        <v>1.3189</v>
-      </c>
-      <c r="V3" s="12">
-        <v>1.3787</v>
-      </c>
-      <c r="W3" s="12">
-        <v>1.3787</v>
-      </c>
-      <c r="X3" s="13">
-        <v>3.524E-2</v>
-      </c>
-      <c r="Y3" s="13">
-        <v>2.7730000000000001E-2</v>
-      </c>
-      <c r="Z3" s="13">
-        <v>2.4570000000000002E-2</v>
-      </c>
-      <c r="AA3" s="13">
-        <v>2.248E-2</v>
-      </c>
-      <c r="AB3" s="13">
-        <v>1.8769999999999998E-2</v>
-      </c>
-      <c r="AC3" s="13">
-        <v>1.8350000000000002E-2</v>
-      </c>
-      <c r="AD3" s="13">
-        <v>1.7819999999999999E-2</v>
-      </c>
-      <c r="AE3" s="13">
-        <v>1.7979999999999999E-2</v>
-      </c>
-      <c r="AF3" s="13">
-        <v>1.8339999999999999E-2</v>
-      </c>
-      <c r="AG3" s="13">
-        <v>1.941E-2</v>
-      </c>
-      <c r="AH3" s="13">
-        <v>2.0570000000000001E-2</v>
-      </c>
-      <c r="AI3" s="13">
-        <v>2.1479999999999999E-2</v>
-      </c>
-      <c r="AJ3" s="13">
-        <v>2.2159999999999999E-2</v>
-      </c>
-      <c r="AK3" s="13">
-        <v>2.2849999999999999E-2</v>
-      </c>
-      <c r="AL3" s="13">
-        <v>2.4209999999999999E-2</v>
-      </c>
-      <c r="AM3" s="13">
-        <v>2.9649999999999999E-2</v>
-      </c>
-      <c r="AN3" s="13">
-        <v>3.755E-2</v>
-      </c>
-      <c r="AO3" s="13">
-        <v>4.4299999999999999E-2</v>
-      </c>
-      <c r="AP3" s="12">
-        <v>1.78E-2</v>
-      </c>
-      <c r="AQ3" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="AR3" s="12">
-        <v>0.12</v>
-      </c>
-      <c r="AS3" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="AT3" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="AU3" s="12">
-        <v>0.12</v>
-      </c>
-      <c r="AV3" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="AW3" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="AX3" s="12">
-        <v>0</v>
-      </c>
-      <c r="AY3" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
       <c r="X4" s="13"/>
       <c r="Y4" s="13"/>
       <c r="Z4" s="13"/>
@@ -4772,7 +4825,7 @@
       <c r="AN4" s="13"/>
       <c r="AO4" s="13"/>
     </row>
-    <row r="21" s="23" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="21" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4782,19 +4835,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51281E0C-C3D7-4E6E-9445-AF10F5AA801D}">
   <dimension ref="A1:U21"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="6" width="8.77734375" style="1"/>
+    <col min="1" max="6" width="8.83203125" style="1"/>
     <col min="7" max="7" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="17" width="8.77734375" style="1"/>
-    <col min="18" max="18" width="10.21875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="8.77734375" style="1"/>
-    <col min="20" max="20" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="8.77734375" style="1"/>
+    <col min="8" max="17" width="8.83203125" style="1"/>
+    <col min="18" max="18" width="10.1640625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="8.83203125" style="1"/>
+    <col min="20" max="20" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
         <v>107</v>
       </c>
@@ -4859,7 +4912,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="str">
         <f>Main_Input!A2</f>
         <v>Config1</v>
@@ -4879,28 +4932,36 @@
       <c r="F2" s="4">
         <v>0</v>
       </c>
-      <c r="G2" s="4"/>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
       <c r="H2" s="4">
         <v>0</v>
       </c>
       <c r="I2" s="4">
         <v>0</v>
       </c>
-      <c r="J2" s="4"/>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
       <c r="K2" s="4">
         <v>0</v>
       </c>
       <c r="L2" s="4">
         <v>0</v>
       </c>
-      <c r="M2" s="4"/>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
       <c r="N2" s="4">
         <v>0</v>
       </c>
       <c r="O2" s="4">
         <v>0</v>
       </c>
-      <c r="P2" s="4"/>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
       <c r="Q2" s="4">
         <v>0</v>
       </c>
@@ -4917,9 +4978,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>221</v>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>222</v>
       </c>
       <c r="B3" s="4">
         <v>0</v>
@@ -4936,28 +4997,36 @@
       <c r="F3" s="4">
         <v>0</v>
       </c>
-      <c r="G3" s="4"/>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
       <c r="H3" s="4">
         <v>0</v>
       </c>
       <c r="I3" s="4">
         <v>0</v>
       </c>
-      <c r="J3" s="4"/>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
       <c r="K3" s="4">
         <v>0</v>
       </c>
       <c r="L3" s="4">
         <v>0</v>
       </c>
-      <c r="M3" s="4"/>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
       <c r="N3" s="4">
         <v>0</v>
       </c>
       <c r="O3" s="4">
         <v>0</v>
       </c>
-      <c r="P3" s="4"/>
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
       <c r="Q3" s="4">
         <v>0</v>
       </c>
@@ -4974,7 +5043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -4997,7 +5066,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -5020,7 +5089,7 @@
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -5043,7 +5112,7 @@
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -5066,7 +5135,7 @@
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -5089,7 +5158,7 @@
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -5112,7 +5181,7 @@
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -5135,7 +5204,7 @@
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -5158,7 +5227,7 @@
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -5181,7 +5250,7 @@
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -5204,7 +5273,7 @@
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -5227,7 +5296,7 @@
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -5250,7 +5319,7 @@
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -5273,7 +5342,7 @@
       <c r="T16" s="4"/>
       <c r="U16" s="4"/>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -5296,7 +5365,7 @@
       <c r="T17" s="4"/>
       <c r="U17" s="4"/>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -5319,7 +5388,7 @@
       <c r="T18" s="4"/>
       <c r="U18" s="4"/>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -5342,7 +5411,7 @@
       <c r="T19" s="4"/>
       <c r="U19" s="4"/>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -5365,7 +5434,7 @@
       <c r="T20" s="4"/>
       <c r="U20" s="4"/>
     </row>
-    <row r="21" spans="1:21" s="24" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:21" s="24" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -5376,18 +5445,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC58F1BF-02F4-4EE1-B48A-F04EDABB7E7E}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.21875" customWidth="1"/>
-    <col min="7" max="8" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" customWidth="1"/>
+    <col min="7" max="8" width="14.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>209</v>
       </c>
@@ -5413,7 +5482,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>20.8</v>
       </c>
@@ -5439,7 +5508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>217</v>
       </c>
@@ -5475,7 +5544,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AB49278-C885-4626-918F-22B9EA08CAD8}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
